--- a/static/file_template/rental_invoice_template.xlsx
+++ b/static/file_template/rental_invoice_template.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Tổng Cộng tiền thuê sau thuế </t>
   </si>
   <si>
-    <t>(Bằng chữ: Một trăm bảy mươi mốt triệu, tám trăm hai mươi năm nghìn, ba trăm chín mươi hai đồng./.)</t>
+    <t>(Bằng chữ: {{total_after_tax_string}}./.)</t>
   </si>
   <si>
     <t>Hà nội , ngày ...... tháng ...... năm 20......</t>
